--- a/out/LSTM-S4_repeat_5_000007.xlsx
+++ b/out/LSTM-S4_repeat_5_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.534689842160187</v>
+        <v>10.67907012395075</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.534689842160187</v>
+        <v>10.67907012395075</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.134689842160187</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.134689842160187</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002170325523652136</v>
+        <v>-6.350885619758629e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.502064716582701</v>
+        <v>0.7321632397323752</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC40" t="n">
-        <v>5.007997325228201</v>
+        <v>1.46545842325624</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3751957880912118</v>
+        <v>0.1097911438137972</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.252965918301224</v>
+        <v>0.9518947012812844</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.4691167591877605</v>
+        <v>0.1372747102358227</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.816063345869661</v>
+        <v>1.116670368164936</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.6724766495555581</v>
+        <v>0.1967826461112384</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC43" t="n">
-        <v>4.692164841330529</v>
+        <v>1.373038420346467</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.7194168109942486</v>
+        <v>0.2105184526747808</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC44" t="n">
-        <v>5.458572323740582</v>
+        <v>1.597307351345162</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.7624375522263873</v>
+        <v>0.2231063901292494</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC45" t="n">
-        <v>6.264084359394666</v>
+        <v>1.833019085469454</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3440738869155326</v>
+        <v>0.1006837643598522</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC46" t="n">
-        <v>6.189160998422606</v>
+        <v>1.811094679552205</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1661713177903906</v>
+        <v>0.04862565627917254</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC47" t="n">
-        <v>6.177161233446059</v>
+        <v>1.807583232453053</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.07917629858761475</v>
+        <v>0.02316867753908389</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC48" t="n">
-        <v>6.169209262420366</v>
+        <v>1.805256255114777</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02345938497980003</v>
+        <v>0.006862180623952113</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC49" t="n">
-        <v>6.136867396074789</v>
+        <v>1.795788932819602</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01551723427697401</v>
+        <v>0.004536897260261469</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC50" t="n">
-        <v>6.144430504614593</v>
+        <v>1.797998640916994</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.007939453618170516</v>
+        <v>0.002320085942499</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC51" t="n">
-        <v>6.144782945991155</v>
+        <v>1.798098252506395</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.004058895048927012</v>
+        <v>0.00118386798434055</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC52" t="n">
-        <v>6.144956556545387</v>
+        <v>1.79814552668101</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001522393762875266</v>
+        <v>0.0004423189860551449</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC53" t="n">
-        <v>6.143940127535647</v>
+        <v>1.79784438854966</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0008274310310539298</v>
+        <v>0.0002383767632912877</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC54" t="n">
-        <v>6.144071813169386</v>
+        <v>1.797879399410737</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0003963386250319559</v>
+        <v>0.0001126200326826326</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC55" t="n">
-        <v>6.144035707495346</v>
+        <v>1.797865283292404</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002429566895936301</v>
+        <v>6.781267869019299e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC56" t="n">
-        <v>6.144126079133475</v>
+        <v>1.797888233616753</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001247005138431669</v>
+        <v>3.308665882696171e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC57" t="n">
-        <v>6.14413242487534</v>
+        <v>1.797886551950965</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.79428672394662e-05</v>
+        <v>1.29836763541332e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC58" t="n">
-        <v>6.14412349858469</v>
+        <v>1.797880408501921</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.593268408840677e-05</v>
+        <v>6.512317399864405e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC59" t="n">
-        <v>6.144136393843576</v>
+        <v>1.797880721933198</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.364978044218695e-05</v>
+        <v>8.280563881834207e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC60" t="n">
-        <v>6.144127733696454</v>
+        <v>1.797874578137222</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>3.234953259883613e-06</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC61" t="n">
-        <v>6.14412054118357</v>
+        <v>1.797868893603194</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.494870763551826e-07</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC62" t="n">
-        <v>6.144116202646297</v>
+        <v>1.79786414232798</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC63" t="n">
-        <v>6.144110624351173</v>
+        <v>1.797858853180418</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.053889915940302e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC64" t="n">
-        <v>6.144105577730105</v>
+        <v>1.797858830446117</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC65" t="n">
-        <v>6.144105896010322</v>
+        <v>1.797859148726333</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC66" t="n">
-        <v>6.144106987256778</v>
+        <v>1.797860239972791</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC67" t="n">
-        <v>6.144106297649643</v>
+        <v>1.797859550365655</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC68" t="n">
-        <v>6.144106327962045</v>
+        <v>1.797859580678056</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC69" t="n">
-        <v>6.144106138509534</v>
+        <v>1.797859391225546</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC70" t="n">
-        <v>6.144106191556237</v>
+        <v>1.797859444272249</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC71" t="n">
-        <v>6.14410624460294</v>
+        <v>1.797859497318952</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC72" t="n">
-        <v>6.144106206712438</v>
+        <v>1.79785945942845</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC73" t="n">
-        <v>6.144106077884731</v>
+        <v>1.797859330600743</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC74" t="n">
-        <v>6.144105933900824</v>
+        <v>1.797859186616836</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC75" t="n">
-        <v>6.144105774760716</v>
+        <v>1.797859027476727</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC76" t="n">
-        <v>6.144105827807418</v>
+        <v>1.79785908052343</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC77" t="n">
-        <v>6.144105774760716</v>
+        <v>1.797859027476727</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC78" t="n">
-        <v>6.144105774760716</v>
+        <v>1.797859027476727</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC79" t="n">
-        <v>6.144105592886306</v>
+        <v>1.797858845602318</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC80" t="n">
-        <v>6.144105759604515</v>
+        <v>1.797859012320526</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC81" t="n">
-        <v>6.144105956635125</v>
+        <v>1.797859209351137</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC82" t="n">
-        <v>6.144105797495016</v>
+        <v>1.797859050211029</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC83" t="n">
-        <v>6.144105835385518</v>
+        <v>1.79785908810153</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC84" t="n">
-        <v>6.144106032416128</v>
+        <v>1.797859285132141</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC85" t="n">
-        <v>6.144106009681828</v>
+        <v>1.79785926239784</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC86" t="n">
-        <v>6.144105858119819</v>
+        <v>1.797859110835832</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC87" t="n">
-        <v>6.144105782338816</v>
+        <v>1.797859035054828</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC88" t="n">
-        <v>6.144105880854122</v>
+        <v>1.797859133570133</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC89" t="n">
-        <v>6.144105888432222</v>
+        <v>1.797859141148233</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC90" t="n">
-        <v>6.144106153665735</v>
+        <v>1.797859406381747</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC91" t="n">
-        <v>6.144105858119819</v>
+        <v>1.797859110835832</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC92" t="n">
-        <v>6.144106100619032</v>
+        <v>1.797859353335044</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC93" t="n">
-        <v>6.144106183978137</v>
+        <v>1.797859436694148</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC94" t="n">
-        <v>6.144106017259928</v>
+        <v>1.79785926997594</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC95" t="n">
-        <v>6.144106206712438</v>
+        <v>1.79785945942845</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC96" t="n">
-        <v>6.144105858119819</v>
+        <v>1.797859110835832</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC97" t="n">
-        <v>6.144105653511109</v>
+        <v>1.797858906227121</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC98" t="n">
-        <v>6.144105767182615</v>
+        <v>1.797859019898627</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC99" t="n">
-        <v>6.144105782338816</v>
+        <v>1.797859035054828</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC100" t="n">
-        <v>6.144105547417704</v>
+        <v>1.797858800133715</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC101" t="n">
-        <v>6.144105608042507</v>
+        <v>1.797858860758518</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC102" t="n">
-        <v>6.1441054792148</v>
+        <v>1.797858731930812</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC103" t="n">
-        <v>6.144105615620608</v>
+        <v>1.797858868336619</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC104" t="n">
-        <v>6.144105789916916</v>
+        <v>1.797859042632928</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC105" t="n">
-        <v>6.144105933900824</v>
+        <v>1.797859186616836</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC106" t="n">
-        <v>6.144105767182615</v>
+        <v>1.797859019898627</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC107" t="n">
-        <v>6.144105759604515</v>
+        <v>1.797859012320526</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC108" t="n">
-        <v>6.144105471636699</v>
+        <v>1.797858724352711</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC109" t="n">
-        <v>6.144105486792901</v>
+        <v>1.797858739508913</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC110" t="n">
-        <v>6.144105714135912</v>
+        <v>1.797858966851924</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC111" t="n">
-        <v>6.144105698979711</v>
+        <v>1.797858951695724</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC112" t="n">
-        <v>6.144105805073117</v>
+        <v>1.797859057789129</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC113" t="n">
-        <v>6.144105532261503</v>
+        <v>1.797858784977515</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC114" t="n">
-        <v>6.144105630776807</v>
+        <v>1.79785888349282</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC115" t="n">
-        <v>6.144105782338816</v>
+        <v>1.797859035054828</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC116" t="n">
-        <v>6.144105797495016</v>
+        <v>1.797859050211029</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC117" t="n">
-        <v>6.144105774760716</v>
+        <v>1.797859027476727</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC118" t="n">
-        <v>6.144105858119819</v>
+        <v>1.797859110835832</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC119" t="n">
-        <v>6.144105956635125</v>
+        <v>1.797859209351137</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC120" t="n">
-        <v>6.144105789916916</v>
+        <v>1.797859042632928</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC121" t="n">
-        <v>6.144105774760716</v>
+        <v>1.797859027476727</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC122" t="n">
-        <v>6.144105744448313</v>
+        <v>1.797858997164326</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC123" t="n">
-        <v>6.144105729292114</v>
+        <v>1.797858982008125</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC124" t="n">
-        <v>6.144105767182615</v>
+        <v>1.797859019898627</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC125" t="n">
-        <v>6.144105782338816</v>
+        <v>1.797859035054828</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC126" t="n">
-        <v>6.144105774760716</v>
+        <v>1.797859027476727</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_5_000007.xlsx
+++ b/out/LSTM-S4_repeat_5_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002170325523652136</v>
+        <v>-0.0001928879555852618</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.502064716582701</v>
+        <v>2.223713250653077</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC40" t="n">
-        <v>5.007997325228201</v>
+        <v>4.450863960680922</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3751957880912118</v>
+        <v>0.3334556987309211</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.252965918301224</v>
+        <v>2.891077623860226</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.4691167591877605</v>
+        <v>0.4169281796219443</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.816063345869661</v>
+        <v>3.391531194090128</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.6724766495555581</v>
+        <v>0.5976644055722461</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC43" t="n">
-        <v>4.692164841330529</v>
+        <v>4.170167442242097</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.7194168109942486</v>
+        <v>0.6393825287253123</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC44" t="n">
-        <v>5.458572323740582</v>
+        <v>4.851313026231156</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.7624375522263873</v>
+        <v>0.6776173446780431</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC45" t="n">
-        <v>6.264084359394666</v>
+        <v>5.567212872864174</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3440738869155326</v>
+        <v>0.3057961048008927</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC46" t="n">
-        <v>6.189160998422606</v>
+        <v>5.500624640466661</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1661713177903906</v>
+        <v>0.1476855417365314</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.534689842160187</v>
+        <v>0.5545324045481114</v>
       </c>
       <c r="JC47" t="n">
-        <v>6.177161233446059</v>
+        <v>5.489959833207609</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.07917629858761475</v>
+        <v>0.07036776375898894</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.1090082255279058</v>
       </c>
       <c r="JC48" t="n">
-        <v>6.169209262420366</v>
+        <v>5.482892536194032</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02345938497980003</v>
+        <v>0.02084947755372802</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC49" t="n">
-        <v>6.136867396074789</v>
+        <v>5.454148772578813</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01551723427697401</v>
+        <v>0.01378987144592854</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC50" t="n">
-        <v>6.144430504614593</v>
+        <v>5.460869913225386</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.007939453618170516</v>
+        <v>0.007055861922713849</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC51" t="n">
-        <v>6.144782945991155</v>
+        <v>5.461182599541736</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.004058895048927012</v>
+        <v>0.003606903749207362</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC52" t="n">
-        <v>6.144956556545387</v>
+        <v>5.461336344815104</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001522393762875266</v>
+        <v>0.001352851541426277</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC53" t="n">
-        <v>6.143940127535647</v>
+        <v>5.460432407746334</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0008274310310539298</v>
+        <v>0.0007350303616009664</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC54" t="n">
-        <v>6.144071813169386</v>
+        <v>5.460548860506948</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0003963386250319559</v>
+        <v>0.0003510390178501311</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC55" t="n">
-        <v>6.144035707495346</v>
+        <v>5.460516235457972</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002429566895936301</v>
+        <v>0.000215405946305449</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC56" t="n">
-        <v>6.144126079133475</v>
+        <v>5.460596031297699</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001247005138431669</v>
+        <v>0.0001102893456383706</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC57" t="n">
-        <v>6.14413242487534</v>
+        <v>5.460601121453648</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.79428672394662e-05</v>
+        <v>5.094921532396995e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC58" t="n">
-        <v>6.14412349858469</v>
+        <v>5.460592628049469</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.593268408840677e-05</v>
+        <v>3.081609857735592e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC59" t="n">
-        <v>6.144136393843576</v>
+        <v>5.460603566790708</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.364978044218695e-05</v>
+        <v>1.131855788691358e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC60" t="n">
-        <v>6.144127733696454</v>
+        <v>5.46059525049047</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>3.234953259883613e-06</v>
+        <v>2.205584102398162e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC61" t="n">
-        <v>6.14412054118357</v>
+        <v>5.460588195635889</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC62" t="n">
-        <v>6.144116202646297</v>
+        <v>5.460583857098616</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC63" t="n">
-        <v>6.144110624351173</v>
+        <v>5.460578278803492</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC64" t="n">
-        <v>6.144105577730105</v>
+        <v>5.460573232182425</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC65" t="n">
-        <v>6.144105896010322</v>
+        <v>5.460573550462641</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC66" t="n">
-        <v>6.144106987256778</v>
+        <v>5.460574641709098</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC67" t="n">
-        <v>6.144106297649643</v>
+        <v>5.460573952101962</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC68" t="n">
-        <v>6.144106327962045</v>
+        <v>5.460573982414364</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC69" t="n">
-        <v>6.144106138509534</v>
+        <v>5.460573792961854</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC70" t="n">
-        <v>6.144106191556237</v>
+        <v>5.460573846008557</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC71" t="n">
-        <v>6.14410624460294</v>
+        <v>5.46057389905526</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC72" t="n">
-        <v>6.144106206712438</v>
+        <v>5.460573861164757</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC73" t="n">
-        <v>6.144106077884731</v>
+        <v>5.46057373233705</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC74" t="n">
-        <v>6.144105933900824</v>
+        <v>5.460573588353143</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC75" t="n">
-        <v>6.144105774760716</v>
+        <v>5.460573429213035</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC76" t="n">
-        <v>6.144105827807418</v>
+        <v>5.460573482259737</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC77" t="n">
-        <v>6.144105774760716</v>
+        <v>5.460573429213035</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC78" t="n">
-        <v>6.144105774760716</v>
+        <v>5.460573429213035</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC79" t="n">
-        <v>6.144105592886306</v>
+        <v>5.460573247338625</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC80" t="n">
-        <v>6.144105759604515</v>
+        <v>5.460573414056834</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC81" t="n">
-        <v>6.144105956635125</v>
+        <v>5.460573611087444</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC82" t="n">
-        <v>6.144105797495016</v>
+        <v>5.460573451947336</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC83" t="n">
-        <v>6.144105835385518</v>
+        <v>5.460573489837837</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC84" t="n">
-        <v>6.144106032416128</v>
+        <v>5.460573686868448</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC85" t="n">
-        <v>6.144106009681828</v>
+        <v>5.460573664134147</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC86" t="n">
-        <v>6.144105858119819</v>
+        <v>5.460573512572139</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC87" t="n">
-        <v>6.144105782338816</v>
+        <v>5.460573436791135</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC88" t="n">
-        <v>6.144105880854122</v>
+        <v>5.460573535306441</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC89" t="n">
-        <v>6.144105888432222</v>
+        <v>5.460573542884541</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC90" t="n">
-        <v>6.144106153665735</v>
+        <v>5.460573808118054</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC91" t="n">
-        <v>6.144105858119819</v>
+        <v>5.460573512572139</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC92" t="n">
-        <v>6.144106100619032</v>
+        <v>5.460573755071351</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC93" t="n">
-        <v>6.144106183978137</v>
+        <v>5.460573838430456</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC94" t="n">
-        <v>6.144106017259928</v>
+        <v>5.460573671712248</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC95" t="n">
-        <v>6.144106206712438</v>
+        <v>5.460573861164757</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC96" t="n">
-        <v>6.144105858119819</v>
+        <v>5.460573512572139</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC97" t="n">
-        <v>6.144105653511109</v>
+        <v>5.460573307963428</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC98" t="n">
-        <v>6.144105767182615</v>
+        <v>5.460573421634934</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC99" t="n">
-        <v>6.144105782338816</v>
+        <v>5.460573436791135</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC100" t="n">
-        <v>6.144105547417704</v>
+        <v>5.460573201870023</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC101" t="n">
-        <v>6.144105608042507</v>
+        <v>5.460573262494826</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC102" t="n">
-        <v>6.1441054792148</v>
+        <v>5.460573133667119</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC103" t="n">
-        <v>6.144105615620608</v>
+        <v>5.460573270072927</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC104" t="n">
-        <v>6.144105789916916</v>
+        <v>5.460573444369235</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC105" t="n">
-        <v>6.144105933900824</v>
+        <v>5.460573588353143</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC106" t="n">
-        <v>6.144105767182615</v>
+        <v>5.460573421634934</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC107" t="n">
-        <v>6.144105759604515</v>
+        <v>5.460573414056834</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC108" t="n">
-        <v>6.144105471636699</v>
+        <v>5.460573126089018</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC109" t="n">
-        <v>6.144105486792901</v>
+        <v>5.46057314124522</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC110" t="n">
-        <v>6.144105714135912</v>
+        <v>5.460573368588231</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC111" t="n">
-        <v>6.144105698979711</v>
+        <v>5.46057335343203</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC112" t="n">
-        <v>6.144105805073117</v>
+        <v>5.460573459525436</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC113" t="n">
-        <v>6.144105532261503</v>
+        <v>5.460573186713822</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC114" t="n">
-        <v>6.144105630776807</v>
+        <v>5.460573285229127</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC115" t="n">
-        <v>6.144105782338816</v>
+        <v>5.460573436791135</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC116" t="n">
-        <v>6.144105797495016</v>
+        <v>5.460573451947336</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC117" t="n">
-        <v>6.144105774760716</v>
+        <v>5.460573429213035</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC118" t="n">
-        <v>6.144105858119819</v>
+        <v>5.460573512572139</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC119" t="n">
-        <v>6.144105956635125</v>
+        <v>5.460573611087444</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC120" t="n">
-        <v>6.144105789916916</v>
+        <v>5.460573444369235</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC121" t="n">
-        <v>6.144105774760716</v>
+        <v>5.460573429213035</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC122" t="n">
-        <v>6.144105744448313</v>
+        <v>5.460573398900633</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC123" t="n">
-        <v>6.144105729292114</v>
+        <v>5.460573383744433</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC124" t="n">
-        <v>6.144105767182615</v>
+        <v>5.460573421634934</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC125" t="n">
-        <v>6.144105782338816</v>
+        <v>5.460573436791135</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC126" t="n">
-        <v>6.144105774760716</v>
+        <v>5.460573429213035</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_5_000007.xlsx
+++ b/out/LSTM-S4_repeat_5_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.003942303359508514</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.218073034624129</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.002280492335557938</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.218073034624129</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.001753274351358414</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.418073034624129</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.001935616135597229</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.418073034624129</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.001756306737661362</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.418073034624129</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.001579307019710541</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.418073034624129</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.001672711223363876</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.418073034624129</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.00194082036614418</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.418073034624129</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.002026651054620743</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.418073034624129</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.002184037119150162</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.218073034624129</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.002265695482492447</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.218073034624129</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.002326007932424545</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.218073034624129</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.002457201480865479</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.218073034624129</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.002397727221250534</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.218073034624129</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.002490110695362091</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.218073034624129</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.002458743751049042</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.218073034624129</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.002544693648815155</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.218073034624129</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.002546951174736023</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.218073034624129</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.00262562558054924</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.218073034624129</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.00281452015042305</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.218073034624129</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.003041040152311325</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.218073034624129</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.003366086632013321</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.218073034624129</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.00333220511674881</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.218073034624129</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.003137100487947464</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.218073034624129</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.002981159836053848</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.218073034624129</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.00282345712184906</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.218073034624129</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.002587396651506424</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.218073034624129</v>
+        <v>-0.16</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.002768531441688538</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.218073034624129</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.00284188985824585</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.218073034624129</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.002699848264455795</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.218073034624129</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.002622433006763458</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.218073034624129</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.002515885978937149</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.218073034624129</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.002525098621845245</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.218073034624129</v>
+        <v>-0.16</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.002500433474779129</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.218073034624129</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.002769865095615387</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.218073034624129</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.003805212676525116</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.218073034624129</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.003599043935537338</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.218073034624129</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.003050006926059723</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.218073034624129</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001928879555852618</v>
+        <v>-0.0001442297056872631</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.223713250653077</v>
+        <v>1.662755492955732</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.002552486956119537</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.218073034624129</v>
+        <v>0.3</v>
       </c>
       <c r="JC40" t="n">
-        <v>4.450863960680922</v>
+        <v>3.328081305828174</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3334556987309211</v>
+        <v>0.2493376033478721</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.001951001584529877</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.218073034624129</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.891077623860226</v>
+        <v>2.161769372984634</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.4169281796219443</v>
+        <v>0.3117531333942921</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.001305874437093735</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.218073034624129</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.391531194090128</v>
+        <v>2.535977632975608</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.5976644055722461</v>
+        <v>0.446896638262141</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.0013754703104496</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.218073034624129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>4.170167442242097</v>
+        <v>3.118193712197221</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.6393825287253123</v>
+        <v>0.4780908817504419</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.001598536968231201</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.218073034624129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>4.851313026231156</v>
+        <v>3.627512157246003</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.6776173446780431</v>
+        <v>0.5066799709751724</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.001847289502620697</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.218073034624129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>5.567212872864174</v>
+        <v>4.162817394577987</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3057961048008927</v>
+        <v>0.2286545814118022</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.001930307596921921</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.218073034624129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>5.500624640466661</v>
+        <v>4.113026870119093</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1476855417365314</v>
+        <v>0.110429711811827</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.0003965944051742554</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.5545324045481114</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>5.489959833207609</v>
+        <v>4.105052370426346</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.07036776375898894</v>
+        <v>0.05261708287207957</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.0005231872200965881</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.1090082255279058</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>5.482892536194032</v>
+        <v>4.099767840511219</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02084947755372802</v>
+        <v>0.01558948000753997</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.001673594117164612</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>5.454148772578813</v>
+        <v>4.078274628887007</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01378987144592854</v>
+        <v>0.01031015333330494</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.002432957291603088</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>5.460869913225386</v>
+        <v>4.083299178444027</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.007055861922713849</v>
+        <v>0.005274903160156426</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.003387816250324249</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>5.461182599541736</v>
+        <v>4.083531734850594</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003606903749207362</v>
+        <v>0.002695874514805839</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.003748919814825058</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>5.461336344815104</v>
+        <v>4.083645439858524</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001352851541426277</v>
+        <v>0.001009982673942385</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.003752004355192184</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>5.460432407746334</v>
+        <v>4.082968241838502</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0007350303616009664</v>
+        <v>0.0005485790107405222</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.003677681088447571</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>5.460548860506948</v>
+        <v>4.083054094460991</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0003510390178501311</v>
+        <v>0.00026123453343704</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.003539081662893295</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>5.460516235457972</v>
+        <v>4.083028429691553</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.000215405946305449</v>
+        <v>0.0001603044597290868</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.003312844783067703</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>5.460596031297699</v>
+        <v>4.083086884481966</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001102893456383706</v>
+        <v>8.146700922877794e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.003598302602767944</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>5.460601121453648</v>
+        <v>4.083089417997475</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.094921532396995e-05</v>
+        <v>3.696191149297746e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.002242919057607651</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>5.460592628049469</v>
+        <v>4.083081820678642</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.081609857735592e-05</v>
+        <v>2.186207393301694e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.002489015460014343</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>5.460603566790708</v>
+        <v>4.083088564442286</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.131855788691358e-05</v>
+        <v>6.65611277636684e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.003756206482648849</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>5.46059525049047</v>
+        <v>4.083081163178829</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>2.205584102398162e-06</v>
+        <v>1.468457874272584e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.004535242915153503</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>5.460588195635889</v>
+        <v>4.083074656452469</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.494870763551826e-07</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.004724174737930298</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>5.460583857098616</v>
+        <v>4.083070152549514</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.004899255931377411</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>5.460578278803492</v>
+        <v>4.083064719418045</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.004722032696008682</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>5.460573232182425</v>
+        <v>4.083059672796978</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.003586981445550919</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>5.460573550462641</v>
+        <v>4.083059991077194</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.001638375222682953</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>5.460574641709098</v>
+        <v>4.083061082323651</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.002072211354970932</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>5.460573952101962</v>
+        <v>4.083060392716515</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.003847051411867142</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>5.460573982414364</v>
+        <v>4.083060423028917</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.005416460335254669</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>5.460573792961854</v>
+        <v>4.083060233576407</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.006519578397274017</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>5.460573846008557</v>
+        <v>4.08306028662311</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.007742393761873245</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>5.46057389905526</v>
+        <v>4.083060339669813</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.008754167705774307</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>5.460573861164757</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.009255092591047287</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>5.46057373233705</v>
+        <v>4.083060172951603</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.009032666683197021</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>5.460573588353143</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.008485730737447739</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>5.460573429213035</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.008081801235675812</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>5.460573482259737</v>
+        <v>4.08305992287429</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.00785570964217186</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>5.460573429213035</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.007638648152351379</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>5.460573429213035</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.007252678275108337</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>5.460573247338625</v>
+        <v>4.083059687953178</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.007167171686887741</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>5.460573414056834</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.007509548217058182</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>5.460573611087444</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.007640961557626724</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>5.460573451947336</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.007279906421899796</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>5.460573489837837</v>
+        <v>4.08305993045239</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.006975036114454269</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>5.460573686868448</v>
+        <v>4.083060127483001</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.007133733481168747</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>5.460573664134147</v>
+        <v>4.0830601047487</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.007376205176115036</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>5.460573512572139</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.007197964936494827</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>5.460573436791135</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.006997305899858475</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>5.460573535306441</v>
+        <v>4.083059975920994</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.006686713546514511</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>5.460573542884541</v>
+        <v>4.083059983499094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.006614532321691513</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>5.460573808118054</v>
+        <v>4.083060248732608</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.006888668984174728</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC91" t="n">
-        <v>5.460573512572139</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.006641816347837448</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>5.460573755071351</v>
+        <v>4.083060195685905</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.006831403821706772</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>5.460573838430456</v>
+        <v>4.083060279045009</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.006191857159137726</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>5.460573671712248</v>
+        <v>4.083060112326801</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.006218072026968002</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>5.460573861164757</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.006591726094484329</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>5.460573512572139</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.006966385990381241</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>5.460573307963428</v>
+        <v>4.083059748577981</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.007054068148136139</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>5.460573421634934</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.006890799850225449</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>5.460573436791135</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.006612781435251236</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC100" t="n">
-        <v>5.460573201870023</v>
+        <v>4.083059642484576</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.006474506109952927</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>5.460573262494826</v>
+        <v>4.083059703109379</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.006326798349618912</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>5.460573133667119</v>
+        <v>4.083059574281672</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.005523540079593658</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>5.460573270072927</v>
+        <v>4.08305971068748</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.005275636911392212</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>5.460573444369235</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.005367118865251541</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>5.460573588353143</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.005323942750692368</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>5.460573421634934</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.005444251000881195</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>5.460573414056834</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.005702648311853409</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC108" t="n">
-        <v>5.460573126089018</v>
+        <v>4.083059566703572</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.005696598440408707</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.16</v>
       </c>
       <c r="JC109" t="n">
-        <v>5.46057314124522</v>
+        <v>4.083059581859773</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.005667500197887421</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.16</v>
       </c>
       <c r="JC110" t="n">
-        <v>5.460573368588231</v>
+        <v>4.083059809202784</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.005408480763435364</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC111" t="n">
-        <v>5.46057335343203</v>
+        <v>4.083059794046584</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.005373857915401459</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>5.460573459525436</v>
+        <v>4.08305990013999</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.005201254040002823</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>5.460573186713822</v>
+        <v>4.083059627328375</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.004721269011497498</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>5.460573285229127</v>
+        <v>4.08305972584368</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.004200559109449387</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>5.460573436791135</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.004105951637029648</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>5.460573451947336</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.004177253693342209</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>5.460573429213035</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.004210971295833588</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>5.460573512572139</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.00438203290104866</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>5.460573611087444</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.004481811076402664</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
-        <v>5.460573444369235</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.004452884197235107</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC121" t="n">
-        <v>5.460573429213035</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.004362951964139938</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC122" t="n">
-        <v>5.460573398900633</v>
+        <v>4.083059839515186</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.004154723137617111</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>5.460573383744433</v>
+        <v>4.083059824358986</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.00415835902094841</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>5.460573421634934</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.004118308424949646</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7725488556039231</v>
+        <v>1</v>
       </c>
       <c r="JC125" t="n">
-        <v>5.460573436791135</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.003923222422599792</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7725488556039231</v>
+        <v>1.14</v>
       </c>
       <c r="JC126" t="n">
-        <v>5.460573429213035</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
   </sheetData>
